--- a/项目管理系统v2.0优化清单.xlsx
+++ b/项目管理系统v2.0优化清单.xlsx
@@ -1,15 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="2.0 优化清单" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求与优化记录（新格式）" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2.0 优化清单" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'需求与优化记录（新格式）'!$A$1:$J$30</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,8 +64,16 @@
       <color rgb="0092400E"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -98,8 +110,13 @@
         <fgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E3A8A"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -121,11 +138,25 @@
         <color rgb="00E2E8F0"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D1D5DB"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,6 +188,27 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -232,6 +284,162 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing_wm1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -518,7 +726,1595 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="62" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>版本号</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>一级页面</t>
+        </is>
+      </c>
+      <c r="C1" s="12" t="inlineStr">
+        <is>
+          <t>二级页面</t>
+        </is>
+      </c>
+      <c r="D1" s="12" t="inlineStr">
+        <is>
+          <t>当前需求</t>
+        </is>
+      </c>
+      <c r="E1" s="12" t="inlineStr">
+        <is>
+          <t>需求时间</t>
+        </is>
+      </c>
+      <c r="F1" s="12" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="G1" s="12" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="H1" s="12" t="inlineStr">
+        <is>
+          <t>更新内容</t>
+        </is>
+      </c>
+      <c r="I1" s="12" t="inlineStr">
+        <is>
+          <t>更新时间</t>
+        </is>
+      </c>
+      <c r="J1" s="12" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>表格视图</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>表头（客户 / 项目分组行）</t>
+        </is>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>可折叠分组表头</t>
+        </is>
+      </c>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G2" s="13" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="H2" s="14" t="inlineStr">
+        <is>
+          <t>客户、项目两层分组表头可独立折叠/展开；支持「全部展开」「全部折叠」一键操作</t>
+        </is>
+      </c>
+      <c r="I2" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J2" s="14" t="inlineStr">
+        <is>
+          <t>涉及文件：app.js / index.html / style.css；原清单序号 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="58" customHeight="1">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>全局（顶部导航）</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>顶部搜索框与表格/日历联动过滤</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>全局搜索</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G3" s="15" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="H3" s="16" t="inlineStr">
+        <is>
+          <t>顶部搜索框按任务名 / 项目名 / 客户名模糊匹配；表格与日历视图实时联动过滤</t>
+        </is>
+      </c>
+      <c r="I3" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J3" s="16" t="inlineStr">
+        <is>
+          <t>涉及文件：app.js / index.html；原清单序号 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="58" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>表格视图</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>表头列宽（列头拖拽手柄）</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>列宽拖拽调节</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>表格列头右侧拖拽手柄可自由调整列宽，最小 50px</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J4" s="14" t="inlineStr">
+        <is>
+          <t>涉及文件：app.js / style.css；原清单序号 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>表格视图</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>任务行单元格（任务名 / 开始时间 / 结束时间）</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>单元格内联编辑</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="H5" s="16" t="inlineStr">
+        <is>
+          <t>点击任务名、开始/结束时间单元格直接进入编辑态，回车保存、Esc 取消</t>
+        </is>
+      </c>
+      <c r="I5" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J5" s="16" t="inlineStr">
+        <is>
+          <t>涉及文件：app.js / style.css；原清单序号 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>日历视图</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>顶部模式切换（月历 / 周历）</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>月历 / 周历双模式</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>顶部一键切换月历、周历；周一起始；显示今日、节假日、调休工作日</t>
+        </is>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J6" s="14" t="inlineStr">
+        <is>
+          <t>涉及文件：app.js / style.css；原清单序号 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>日历视图</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>月视图任务条泳道、周视图内容区</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>跨天任务横条 + 泳道布局</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="H7" s="16" t="inlineStr">
+        <is>
+          <t>任务以横条显示跨天区间，自动贪心分配泳道避免重叠；含阶段的任务条加高</t>
+        </is>
+      </c>
+      <c r="I7" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t>涉及文件：app.js / style.css；原清单序号 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>日历视图</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>任务条（拖拽移动 / 右边缘拉伸）</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>任务拖拽与拉伸</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t>拖拽任务条移动日期区间；拖拽右侧手柄拉伸结束日期</t>
+        </is>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J8" s="14" t="inlineStr">
+        <is>
+          <t>涉及文件：app.js / style.css；原清单序号 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>日历视图</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>任务条内阶段迷你条</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>任务阶段迷你条</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G9" s="15" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="H9" s="16" t="inlineStr">
+        <is>
+          <t>含阶段的任务在任务条内显示按日期定位的阶段迷你条</t>
+        </is>
+      </c>
+      <c r="I9" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <t>涉及文件：app.js / style.css；原清单序号 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>全局（筛选栏）</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>项目多选下拉框</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>多选下拉框</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>支持多选项目过滤日历视图任务；空集合表示全部项目</t>
+        </is>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>涉及文件：app.js / style.css；原清单序号 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>全局（筛选栏）</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>常用项目 chip 与添加下拉</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>常用项目快捷按钮（可增删）</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="H11" s="16" t="inlineStr">
+        <is>
+          <t>常用项目以 chip 形式展示，一键切换；可增删常用项，localStorage 持久化</t>
+        </is>
+      </c>
+      <c r="I11" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J11" s="16" t="inlineStr">
+        <is>
+          <t>涉及文件：app.js / style.css；原清单序号 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>任务编辑弹窗</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>阶段列表（增删阶段、名称与起止日期）</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>任务阶段编辑器</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>任务弹窗中可动态增删多个阶段（名称 + 起止日期），仅日历视图与弹窗展示</t>
+        </is>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>涉及文件：app.js / index.html；原清单序号 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>任务编辑弹窗</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>日期区（仅工作日执行勾选）</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>仅工作日执行</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G13" s="15" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="H13" s="16" t="inlineStr">
+        <is>
+          <t>勾选后自动跳过休息日/周末/节假日，调休工作日照常计入</t>
+        </is>
+      </c>
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J13" s="16" t="inlineStr">
+        <is>
+          <t>涉及文件：app.js；原清单序号 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>全局（任务展示）</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>任务名称后的工作日数标注</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>工作日数标注</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="H14" s="14" t="inlineStr">
+        <is>
+          <t>任务名后显示「（N）」标注花费工作日数</t>
+        </is>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>涉及文件：app.js / style.css；原清单序号 13</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>归档视图</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>顶部搜索、批量恢复、排序下拉</t>
+        </is>
+      </c>
+      <c r="D15" s="16" t="inlineStr">
+        <is>
+          <t>归档搜索 + 批量恢复 + 排序</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G15" s="15" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="H15" s="16" t="inlineStr">
+        <is>
+          <t>归档视图支持关键词搜索、全选批量恢复、按结束/开始/任务名/品牌排序</t>
+        </is>
+      </c>
+      <c r="I15" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J15" s="16" t="inlineStr">
+        <is>
+          <t>涉及文件：app.js / style.css；原清单序号 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>表格视图</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>任务行拖拽手柄与跨环节移动</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>任务行拖拽排序与跨环节移动</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="H16" s="14" t="inlineStr">
+        <is>
+          <t>任务行可拖拽到同环节任意位置或跨环节移动，自动展开目标环节</t>
+        </is>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
+        <is>
+          <t>涉及文件：app.js / style.css；原清单序号 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>全局（数据与同步）</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>同步面板（GitHub Token / Gist）</t>
+        </is>
+      </c>
+      <c r="D17" s="16" t="inlineStr">
+        <is>
+          <t>GitHub Gist 跨设备同步</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G17" s="15" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="H17" s="16" t="inlineStr">
+        <is>
+          <t>通过私有 Gist 推送/拉取数据；首次推送自动创建并保存 Gist ID；本地保存 Token</t>
+        </is>
+      </c>
+      <c r="I17" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J17" s="16" t="inlineStr">
+        <is>
+          <t>涉及文件：app.js / index.html；原清单序号 16</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>日历视图</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>日期格（休息日 / 调休上班标记）</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>2026 法定节假日与调休工作日</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="H18" s="14" t="inlineStr">
+        <is>
+          <t>内置 2026 全年法定节假日（休息日）与调休工作日；日历自动标记</t>
+        </is>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>涉及文件：app.js；原清单序号 17</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>日历视图</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>日期格节假日名称标签</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>节假日名称展示</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="15" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G19" s="15" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="H19" s="16" t="inlineStr">
+        <is>
+          <t>日历格子显示节假日名称（元旦、春节、清明、劳动节等）</t>
+        </is>
+      </c>
+      <c r="I19" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J19" s="16" t="inlineStr">
+        <is>
+          <t>涉及文件：app.js；原清单序号 18</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>全局（左侧项目结构）</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>侧栏折叠按钮与拖拽调宽边缘</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>侧栏折叠与宽度拖拽</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="H20" s="14" t="inlineStr">
+        <is>
+          <t>左侧项目结构树可一键收起/展开；可拖拽侧栏边缘调节宽度</t>
+        </is>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>涉及文件：app.js / index.html / style.css；原清单序号 19</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>全局（左侧项目结构）</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>环节颜色圆点与预设色板</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>环节颜色选择器</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G21" s="15" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="H21" s="16" t="inlineStr">
+        <is>
+          <t>点击环节颜色圆点弹出预设色板，可一键修改同名环节颜色</t>
+        </is>
+      </c>
+      <c r="I21" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J21" s="16" t="inlineStr">
+        <is>
+          <t>涉及文件：app.js / style.css；原清单序号 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>全局（任务展示）</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>已归档任务行样式（置灰 + 删除线）</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>已归档任务行置灰</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="H22" s="14" t="inlineStr">
+        <is>
+          <t>列表/日历中已归档任务自动置灰、删除线样式</t>
+        </is>
+      </c>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr">
+        <is>
+          <t>涉及文件：app.js / style.css；原清单序号 21</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>表格视图</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>行尾操作列（删除）</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
+        <is>
+          <t>表格新增「删除」列</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G23" s="15" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="H23" s="16" t="inlineStr">
+        <is>
+          <t>表格视图新增删除列，任务行、项目行均可一键删除；项目删除提示子节点数量</t>
+        </is>
+      </c>
+      <c r="I23" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t>涉及文件：app.js；原清单序号 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>任务编辑弹窗</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>底部操作区（删除任务按钮）</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>任务弹窗删除按钮</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="H24" s="14" t="inlineStr">
+        <is>
+          <t>任务编辑弹窗底部新增红色「删除任务」按钮（仅编辑时显示，新建时隐藏）</t>
+        </is>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="inlineStr">
+        <is>
+          <t>涉及文件：app.js / index.html；原清单序号 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>表格视图</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>项目分组头拖拽手柄（同客户内排序）</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="inlineStr">
+        <is>
+          <t>列表视图项目拖拽排序</t>
+        </is>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G25" s="15" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="H25" s="16" t="inlineStr">
+        <is>
+          <t>项目分组头新增拖拽手柄，支持同一客户下项目互相拖拽排序，绿边高亮插入位置</t>
+        </is>
+      </c>
+      <c r="I25" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>涉及文件：app.js / style.css；原清单序号 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>表格视图</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>页面底部固定隐藏栏</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>底部固定隐藏栏</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="H26" s="14" t="inlineStr">
+        <is>
+          <t>列表视图底部新增固定吸附的「隐藏栏」，不随页面上下滑动变化</t>
+        </is>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J26" s="14" t="inlineStr">
+        <is>
+          <t>涉及文件：app.js / index.html / style.css；原清单序号 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>表格视图</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>项目行操作（隐藏）与隐藏栏（恢复）</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="inlineStr">
+        <is>
+          <t>项目隐藏 / 恢复</t>
+        </is>
+      </c>
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F27" s="15" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G27" s="15" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="H27" s="16" t="inlineStr">
+        <is>
+          <t>项目行「编辑项目信息」后新增「隐藏」按钮，点击移入隐藏栏；隐藏栏可一键「恢复」</t>
+        </is>
+      </c>
+      <c r="I27" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J27" s="16" t="inlineStr">
+        <is>
+          <t>涉及文件：app.js；原清单序号 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>表格视图</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>隐藏栏卡片（隐藏时间、展开详情）</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>隐藏时间记录与详情查看</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="H28" s="14" t="inlineStr">
+        <is>
+          <t>隐藏栏记录项目被隐藏的时间戳；可展开查看项目信息、环节、任务详情</t>
+        </is>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J28" s="14" t="inlineStr">
+        <is>
+          <t>涉及文件：app.js / style.css；原清单序号 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>归档视图</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>列表列（归档时间）</t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="inlineStr">
+        <is>
+          <t>归档时间列</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G29" s="15" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="H29" s="16" t="inlineStr">
+        <is>
+          <t>归档列表新增「归档时间」列，记录任务被归档的时间（精确到分钟）</t>
+        </is>
+      </c>
+      <c r="I29" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J29" s="16" t="inlineStr">
+        <is>
+          <t>涉及文件：app.js；原清单序号 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>归档视图</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>排序下拉（按归档时间）</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>按归档时间排序</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="H30" s="14" t="inlineStr">
+        <is>
+          <t>归档排序下拉新增「按归档时间」选项并设为默认；toggleTaskArchived/saveTaskModal 同步维护 archivedAt</t>
+        </is>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J30" s="14" t="inlineStr">
+        <is>
+          <t>涉及文件：app.js；原清单序号 29</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J30"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -1305,5 +3101,157 @@
     <mergeCell ref="A24:E24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="88" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>字段</t>
+        </is>
+      </c>
+      <c r="B1" s="17" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>版本号</t>
+        </is>
+      </c>
+      <c r="B2" s="18" t="inlineStr">
+        <is>
+          <t>v2.0 为原优化清单批次（含「本轮新增优化」收尾项）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>一级页面</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>功能所属页面：表格视图 / 日历视图 / 归档视图 / 任务编辑弹窗 / 全局（顶部导航、筛选栏、左侧项目结构、任务展示、数据与同步）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>二级页面</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>该需求落在页面中的具体位置，如：表头、任务行、任务条、日期格、侧栏边缘等</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>当前需求</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>即原清单的「优化项」</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>需求时间</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>原清单未记录日期，统一以「—」占位，可自行补充</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>原清单无优先级字段，此处按功能影响面与使用频率归纳为 高/中/低，可按实际调整</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>原清单描述的功能均已实现，统一标为「已完成」</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>更新内容</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>即原清单的「功能描述」，为实际落地内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>更新时间</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>原清单未记录日期，统一以「—」占位</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>原清单的「涉及文件」与原序号，便于回溯</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>